--- a/價格整理.xlsx
+++ b/價格整理.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G218"/>
+  <dimension ref="A1:G221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026/02/22</t>
+          <t>2026/03/02</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -483,28 +483,28 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>G008</t>
+          <t>L063</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>粗蓮花銀48支(本次未叫貨-參考)</t>
+          <t>竹彩面大壽金20支K1</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G2" t="n">
-        <v>225</v>
+        <v>420</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026/02/22</t>
+          <t>2026/03/02</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -512,28 +512,28 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>G007</t>
+          <t>L052</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>粗蓮花金48支</t>
+          <t>竹蓮花銀30支G6</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>225</v>
+        <v>290</v>
       </c>
       <c r="G3" t="n">
-        <v>225</v>
+        <v>580</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026/02/22</t>
+          <t>2026/03/02</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -541,22 +541,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LS26</t>
+          <t>L051</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>環保炮1000公分12入</t>
+          <t>竹蓮花金30支G6</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>2200</v>
+        <v>290</v>
       </c>
       <c r="G4" t="n">
-        <v>2200</v>
+        <v>870</v>
       </c>
     </row>
     <row r="5">
@@ -570,28 +570,28 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>L063</t>
+          <t>G008</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>竹彩面大壽金20支K1</t>
+          <t>粗蓮花銀48支(本次未叫貨-參考)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="G5" t="n">
-        <v>630</v>
+        <v>225</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026/02/21</t>
+          <t>2026/02/22</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -599,28 +599,28 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>L057</t>
+          <t>G007</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>竹彩面土地公18支</t>
+          <t>粗蓮花金48支</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>320</v>
+        <v>225</v>
       </c>
       <c r="G6" t="n">
-        <v>960</v>
+        <v>225</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026/02/21</t>
+          <t>2026/02/22</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -628,28 +628,28 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>L056</t>
+          <t>LS26</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>竹彩面五路18支</t>
+          <t>環保炮1000公分12入</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>320</v>
+        <v>2200</v>
       </c>
       <c r="G7" t="n">
-        <v>960</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026/02/21</t>
+          <t>2026/02/22</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -657,28 +657,28 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>L055</t>
+          <t>L063</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>竹壽金(5只)30支</t>
+          <t>竹彩面大壽金20支K1</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>290</v>
+        <v>210</v>
       </c>
       <c r="G8" t="n">
-        <v>2900</v>
+        <v>630</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026/02/14</t>
+          <t>2026/02/21</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -686,28 +686,28 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>L052</t>
+          <t>L057</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>竹蓮花銀30支G6</t>
+          <t>竹彩面土地公18支</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="G9" t="n">
-        <v>290</v>
+        <v>960</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026/02/14</t>
+          <t>2026/02/21</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -715,28 +715,28 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>L039</t>
+          <t>L056</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>台北環保福金48支</t>
+          <t>竹彩面五路18支</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>120</v>
+        <v>320</v>
       </c>
       <c r="G10" t="n">
-        <v>360</v>
+        <v>960</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026/02/14</t>
+          <t>2026/02/21</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -744,22 +744,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>L068</t>
+          <t>L055</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>(小)竹四方金48支G5-S</t>
+          <t>竹壽金(5只)30支</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>230</v>
+        <v>290</v>
       </c>
       <c r="G11" t="n">
-        <v>3450</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="12">
@@ -773,22 +773,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>L074</t>
+          <t>L052</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>竹小往生24入</t>
+          <t>竹蓮花銀30支G6</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>230</v>
+        <v>290</v>
       </c>
       <c r="G12" t="n">
-        <v>1150</v>
+        <v>290</v>
       </c>
     </row>
     <row r="13">
@@ -802,28 +802,28 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>WA05</t>
+          <t>L039</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5號旺(鳳梨蠟燭)10對</t>
+          <t>台北環保福金48支</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
-        <v>400</v>
+        <v>120</v>
       </c>
       <c r="G13" t="n">
-        <v>400</v>
+        <v>360</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026/02/13</t>
+          <t>2026/02/14</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -831,28 +831,28 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>RD03</t>
+          <t>L068</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>東加A香環60盒T-15</t>
+          <t>(小)竹四方金48支G5-S</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F14" t="n">
-        <v>2480</v>
+        <v>230</v>
       </c>
       <c r="G14" t="n">
-        <v>2480</v>
+        <v>3450</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026/02/12</t>
+          <t>2026/02/14</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -860,28 +860,28 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PE504</t>
+          <t>WA05</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>504五路6盒</t>
+          <t>5號旺(鳳梨蠟燭)10對</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="G15" t="n">
-        <v>1400</v>
+        <v>400</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026/02/12</t>
+          <t>2026/02/14</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -889,28 +889,28 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>D003</t>
+          <t>L074</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>(紅)補運錢40支</t>
+          <t>竹小往生24入</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F16" t="n">
-        <v>310</v>
+        <v>230</v>
       </c>
       <c r="G16" t="n">
-        <v>2480</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026/02/12</t>
+          <t>2026/02/13</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -918,22 +918,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>L069</t>
+          <t>RD03</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>(小)竹福金50支G9-S</t>
+          <t>東加A香環60盒T-15</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>230</v>
+        <v>2480</v>
       </c>
       <c r="G17" t="n">
-        <v>2300</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="18">
@@ -947,22 +947,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>L055</t>
+          <t>PE504</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>竹壽金(5只)30支</t>
+          <t>504五路6盒</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>290</v>
+        <v>700</v>
       </c>
       <c r="G18" t="n">
-        <v>2900</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="19">
@@ -976,22 +976,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>L051</t>
+          <t>D003</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>竹蓮花金30支G6</t>
+          <t>(紅)補運錢40支</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F19" t="n">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="G19" t="n">
-        <v>1450</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="20">
@@ -1005,22 +1005,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>L052</t>
+          <t>L069</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>竹蓮花銀30支G6</t>
+          <t>(小)竹福金50支G9-S</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>290</v>
+        <v>230</v>
       </c>
       <c r="G20" t="n">
-        <v>1450</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="21">
@@ -1063,22 +1063,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PE505</t>
+          <t>L055</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>505土地公6盒</t>
+          <t>竹壽金(5只)30支</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F22" t="n">
-        <v>700</v>
+        <v>290</v>
       </c>
       <c r="G22" t="n">
-        <v>1400</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="23">
@@ -1092,22 +1092,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>G002</t>
+          <t>L052</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>台中粗四方60支</t>
+          <t>竹蓮花銀30支G6</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>205</v>
+        <v>290</v>
       </c>
       <c r="G23" t="n">
-        <v>820</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="24">
@@ -1121,22 +1121,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PE304</t>
+          <t>L051</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>304大金元寶100盒</t>
+          <t>竹蓮花金30支G6</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F24" t="n">
-        <v>20</v>
+        <v>290</v>
       </c>
       <c r="G24" t="n">
-        <v>400</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="25">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PE306</t>
+          <t>PE505</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>306大金條100盒</t>
+          <t>505土地公6盒</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
-        <v>15</v>
+        <v>700</v>
       </c>
       <c r="G25" t="n">
-        <v>300</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="26">
@@ -1179,22 +1179,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NIL0212</t>
+          <t>G002</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>竹大壽金20支</t>
+          <t>台中粗四方60支</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F26" t="n">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="G26" t="n">
-        <v>420</v>
+        <v>820</v>
       </c>
     </row>
     <row r="27">
@@ -1208,28 +1208,28 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>G001</t>
+          <t>PE304</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>台中粗壽金30支</t>
+          <t>304大金元寶100盒</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F27" t="n">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="G27" t="n">
-        <v>1025</v>
+        <v>400</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026/02/11</t>
+          <t>2026/02/12</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1237,28 +1237,28 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>百豐002431</t>
+          <t>PE306</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>紅色花袋1斤10包/串</t>
+          <t>306大金條100盒</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F28" t="n">
-        <v>108</v>
+        <v>15</v>
       </c>
       <c r="G28" t="n">
-        <v>324</v>
+        <v>300</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026/02/11</t>
+          <t>2026/02/12</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1266,28 +1266,28 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>YE23</t>
+          <t>NIL0212</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>三元中往雙面(紅邊)</t>
+          <t>竹大壽金20支</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
-        <v>370</v>
+        <v>210</v>
       </c>
       <c r="G29" t="n">
-        <v>370</v>
+        <v>420</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026/02/11</t>
+          <t>2026/02/12</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1295,22 +1295,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>L068</t>
+          <t>G001</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>(小)竹四方金48支G5-S</t>
+          <t>台中粗壽金30支</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F30" t="n">
-        <v>230</v>
+        <v>205</v>
       </c>
       <c r="G30" t="n">
-        <v>4600</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="31">
@@ -1324,22 +1324,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>TT04</t>
+          <t>百豐002431</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>小元寶400入</t>
+          <t>紅色花袋1斤10包/串</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F31" t="n">
-        <v>800</v>
+        <v>108</v>
       </c>
       <c r="G31" t="n">
-        <v>800</v>
+        <v>324</v>
       </c>
     </row>
     <row r="32">
@@ -1353,22 +1353,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>百豐002430</t>
+          <t>YE23</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>紅色花袋半斤10包/串</t>
+          <t>三元中往雙面(紅邊)</t>
         </is>
       </c>
       <c r="E32" t="n">
         <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>108</v>
+        <v>370</v>
       </c>
       <c r="G32" t="n">
-        <v>108</v>
+        <v>370</v>
       </c>
     </row>
     <row r="33">
@@ -1382,22 +1382,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TT03</t>
+          <t>L068</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>小金條400入</t>
+          <t>(小)竹四方金48支G5-S</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F33" t="n">
-        <v>800</v>
+        <v>230</v>
       </c>
       <c r="G33" t="n">
-        <v>800</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="34">
@@ -1411,22 +1411,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>百豐002432</t>
+          <t>TT04</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>紅色花袋2斤10包/串</t>
+          <t>小元寶400入</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>108</v>
+        <v>800</v>
       </c>
       <c r="G34" t="n">
-        <v>216</v>
+        <v>800</v>
       </c>
     </row>
     <row r="35">
@@ -1440,22 +1440,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>百豐002433</t>
+          <t>百豐002430</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>紅色花袋3斤10包/串</t>
+          <t>紅色花袋半斤10包/串</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
         <v>108</v>
       </c>
       <c r="G35" t="n">
-        <v>216</v>
+        <v>108</v>
       </c>
     </row>
     <row r="36">
@@ -1469,22 +1469,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>百豐002434</t>
+          <t>TT03</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>紅色花袋4斤10包/串</t>
+          <t>小金條400入</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>108</v>
+        <v>800</v>
       </c>
       <c r="G36" t="n">
-        <v>216</v>
+        <v>800</v>
       </c>
     </row>
     <row r="37">
@@ -1498,28 +1498,28 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>百豐002435</t>
+          <t>百豐002432</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>紅色花袋5斤10包/串</t>
+          <t>紅色花袋2斤10包/串</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" t="n">
         <v>108</v>
       </c>
       <c r="G37" t="n">
-        <v>108</v>
+        <v>216</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026/02/10</t>
+          <t>2026/02/11</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1527,28 +1527,28 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>RD22</t>
+          <t>百豐002433</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>(三元)TG2-沉-香環60盒紫S-08</t>
+          <t>紅色花袋3斤10包/串</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="F38" t="n">
-        <v>300</v>
+        <v>108</v>
       </c>
       <c r="G38" t="n">
-        <v>-300</v>
+        <v>216</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026/02/10</t>
+          <t>2026/02/11</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1556,28 +1556,28 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>RD21</t>
+          <t>百豐002434</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>(三元)TG1-沉-香環60盒藍S-05</t>
+          <t>紅色花袋4斤10包/串</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="F39" t="n">
-        <v>200</v>
+        <v>108</v>
       </c>
       <c r="G39" t="n">
-        <v>-200</v>
+        <v>216</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026/02/10</t>
+          <t>2026/02/11</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1585,22 +1585,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>RD20</t>
+          <t>百豐002435</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>(三元)東加-老山-AA香環60盒S-07</t>
+          <t>紅色花袋5斤10包/串</t>
         </is>
       </c>
       <c r="E40" t="n">
         <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>150</v>
+        <v>108</v>
       </c>
       <c r="G40" t="n">
-        <v>150</v>
+        <v>108</v>
       </c>
     </row>
     <row r="41">
@@ -1614,22 +1614,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>WA03</t>
+          <t>RD22</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3號旺(鳳梨蠟燭)12對</t>
+          <t>(三元)TG2-沉-香環60盒紫S-08</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="F41" t="n">
-        <v>520</v>
+        <v>300</v>
       </c>
       <c r="G41" t="n">
-        <v>1040</v>
+        <v>-300</v>
       </c>
     </row>
     <row r="42">
@@ -1643,28 +1643,28 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>L044</t>
+          <t>RD21</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>竹神甲馬20支</t>
+          <t>(三元)TG1-沉-香環60盒藍S-05</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="F42" t="n">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="G42" t="n">
-        <v>615</v>
+        <v>-200</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026/02/09</t>
+          <t>2026/02/10</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1672,28 +1672,28 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PE118</t>
+          <t>RD20</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>118長版五彩發財36盒</t>
+          <t>(三元)東加-老山-AA香環60盒S-07</t>
         </is>
       </c>
       <c r="E43" t="n">
         <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>660</v>
+        <v>150</v>
       </c>
       <c r="G43" t="n">
-        <v>660</v>
+        <v>150</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026/02/09</t>
+          <t>2026/02/10</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1701,28 +1701,28 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>L067</t>
+          <t>WA03</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>(小)竹壽金(十面)20支</t>
+          <t>3號旺(鳳梨蠟燭)12對</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F44" t="n">
-        <v>230</v>
+        <v>520</v>
       </c>
       <c r="G44" t="n">
-        <v>2300</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026/02/09</t>
+          <t>2026/02/10</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1730,22 +1730,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>L069</t>
+          <t>L044</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>(小)竹福金50支G9-S</t>
+          <t>竹神甲馬20支</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F45" t="n">
-        <v>230</v>
+        <v>205</v>
       </c>
       <c r="G45" t="n">
-        <v>2300</v>
+        <v>615</v>
       </c>
     </row>
     <row r="46">
@@ -1759,22 +1759,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>L074</t>
+          <t>PE118</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>竹小往生24入</t>
+          <t>118長版五彩發財36盒</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>230</v>
+        <v>660</v>
       </c>
       <c r="G46" t="n">
-        <v>1150</v>
+        <v>660</v>
       </c>
     </row>
     <row r="47">
@@ -1788,22 +1788,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>L055</t>
+          <t>L067</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>竹壽金(5只)30支</t>
+          <t>(小)竹壽金(十面)20支</t>
         </is>
       </c>
       <c r="E47" t="n">
         <v>10</v>
       </c>
       <c r="F47" t="n">
-        <v>290</v>
+        <v>230</v>
       </c>
       <c r="G47" t="n">
-        <v>2900</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="48">
@@ -1817,22 +1817,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>L045</t>
+          <t>L068</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>竹庫錢50支</t>
+          <t>(小)竹四方金48支G5-S</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F48" t="n">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="G48" t="n">
-        <v>975</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="49">
@@ -1846,22 +1846,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PE173</t>
+          <t>L069</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>173地基紅包30入</t>
+          <t>(小)竹福金50支G9-S</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F49" t="n">
-        <v>900</v>
+        <v>230</v>
       </c>
       <c r="G49" t="n">
-        <v>900</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="50">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>L068</t>
+          <t>L074</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>(小)竹四方金48支G5-S</t>
+          <t>竹小往生24入</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F50" t="n">
         <v>230</v>
       </c>
       <c r="G50" t="n">
-        <v>2300</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="51">
@@ -1904,22 +1904,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>N009</t>
+          <t>L045</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>飯春(300支)</t>
+          <t>竹庫錢50支</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F51" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="G51" t="n">
-        <v>130</v>
+        <v>975</v>
       </c>
     </row>
     <row r="52">
@@ -1933,22 +1933,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>RE02</t>
+          <t>PE173</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>尺6(本色)桂香40斤</t>
+          <t>173地基紅包30入</t>
         </is>
       </c>
       <c r="E52" t="n">
         <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>1080</v>
+        <v>900</v>
       </c>
       <c r="G52" t="n">
-        <v>1080</v>
+        <v>900</v>
       </c>
     </row>
     <row r="53">
@@ -1962,22 +1962,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>RA08</t>
+          <t>L055</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2尺八方螺旋香12hr</t>
+          <t>竹壽金(5只)30支</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F53" t="n">
-        <v>350</v>
+        <v>290</v>
       </c>
       <c r="G53" t="n">
-        <v>1050</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="54">
@@ -1991,22 +1991,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>WA01</t>
+          <t>N009</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1號旺(鳳梨蠟燭)3對</t>
+          <t>飯春(300支)</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F54" t="n">
-        <v>520</v>
+        <v>130</v>
       </c>
       <c r="G54" t="n">
-        <v>3120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="55">
@@ -2049,28 +2049,28 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>WA02</t>
+          <t>RE02</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2號旺(鳳梨蠟燭)6對</t>
+          <t>尺6(本色)桂香40斤</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
-        <v>520</v>
+        <v>1080</v>
       </c>
       <c r="G56" t="n">
-        <v>3120</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026/02/03</t>
+          <t>2026/02/09</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2078,28 +2078,28 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>E001</t>
+          <t>RA08</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>太極(5張)</t>
+          <t>2尺八方螺旋香12hr</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F57" t="n">
-        <v>720</v>
+        <v>350</v>
       </c>
       <c r="G57" t="n">
-        <v>720</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026/02/03</t>
+          <t>2026/02/09</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -2107,28 +2107,28 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>J019</t>
+          <t>WA01</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>(四方)地藏王30支</t>
+          <t>1號旺(鳳梨蠟燭)3對</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F58" t="n">
-        <v>390</v>
+        <v>520</v>
       </c>
       <c r="G58" t="n">
-        <v>780</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026/02/03</t>
+          <t>2026/02/09</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>L052</t>
+          <t>WA02</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>竹蓮花銀30支G6</t>
+          <t>2號旺(鳳梨蠟燭)6對</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F59" t="n">
-        <v>290</v>
+        <v>520</v>
       </c>
       <c r="G59" t="n">
-        <v>1450</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="60">
@@ -2165,22 +2165,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>L051</t>
+          <t>E001</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>竹蓮花金30支G6</t>
+          <t>太極(5張)</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F60" t="n">
-        <v>290</v>
+        <v>720</v>
       </c>
       <c r="G60" t="n">
-        <v>1450</v>
+        <v>720</v>
       </c>
     </row>
     <row r="61">
@@ -2194,22 +2194,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>PE505</t>
+          <t>J019</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>505土地公補財庫盒裝6盒</t>
+          <t>(四方)地藏王30支</t>
         </is>
       </c>
       <c r="E61" t="n">
         <v>2</v>
       </c>
       <c r="F61" t="n">
-        <v>700</v>
+        <v>390</v>
       </c>
       <c r="G61" t="n">
-        <v>1400</v>
+        <v>780</v>
       </c>
     </row>
     <row r="62">
@@ -2223,28 +2223,28 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>LS26</t>
+          <t>L052</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1000公分環保炮12入</t>
+          <t>竹蓮花銀30支G6</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F62" t="n">
-        <v>2200</v>
+        <v>290</v>
       </c>
       <c r="G62" t="n">
-        <v>2200</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026/01/29</t>
+          <t>2026/02/03</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -2252,28 +2252,28 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>大甲金筒15</t>
+          <t>L051</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>報價-大甲金筒BA(13*20)(一般)</t>
+          <t>竹蓮花金30支G6</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F63" t="n">
-        <v>1400</v>
+        <v>290</v>
       </c>
       <c r="G63" t="n">
-        <v>1400</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026/01/29</t>
+          <t>2026/02/03</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -2281,28 +2281,28 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>大甲金筒22-1</t>
+          <t>PE505</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>報價-大甲金筒3As(B)(蓋子)</t>
+          <t>505土地公補財庫盒裝6盒</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64" t="n">
-        <v>70</v>
+        <v>700</v>
       </c>
       <c r="G64" t="n">
-        <v>70</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026/01/29</t>
+          <t>2026/02/03</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>大甲金筒22</t>
+          <t>LS26</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>報價-大甲金筒3As(B)</t>
+          <t>1000公分環保炮12入</t>
         </is>
       </c>
       <c r="E65" t="n">
         <v>1</v>
       </c>
       <c r="F65" t="n">
-        <v>350</v>
+        <v>2200</v>
       </c>
       <c r="G65" t="n">
-        <v>350</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="66">
@@ -2339,22 +2339,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>大甲金筒21</t>
+          <t>大甲金筒16</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>報價-大甲金筒VBA(15*20)(快速)</t>
+          <t>報價-大甲金筒BA(15*20)(一般)</t>
         </is>
       </c>
       <c r="E66" t="n">
         <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>1900</v>
+        <v>1500</v>
       </c>
       <c r="G66" t="n">
-        <v>1900</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="67">
@@ -2397,22 +2397,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>大甲金筒20</t>
+          <t>大甲金筒22-1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>報價-大甲金筒VBA(13*20)(快速)</t>
+          <t>報價-大甲金筒3As(B)(蓋子)</t>
         </is>
       </c>
       <c r="E68" t="n">
         <v>1</v>
       </c>
       <c r="F68" t="n">
-        <v>1800</v>
+        <v>70</v>
       </c>
       <c r="G68" t="n">
-        <v>1800</v>
+        <v>70</v>
       </c>
     </row>
     <row r="69">
@@ -2426,22 +2426,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>大甲金筒19</t>
+          <t>大甲金筒22</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>報價-大甲金筒CBA(15*20)(快速)</t>
+          <t>報價-大甲金筒3As(B)</t>
         </is>
       </c>
       <c r="E69" t="n">
         <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>1600</v>
+        <v>350</v>
       </c>
       <c r="G69" t="n">
-        <v>1600</v>
+        <v>350</v>
       </c>
     </row>
     <row r="70">
@@ -2455,22 +2455,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>大甲金筒18</t>
+          <t>大甲金筒23-1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>報價-大甲金筒CBA(13*20)(快速)</t>
+          <t>報價-大甲金筒3A(小)(B)(蓋子)</t>
         </is>
       </c>
       <c r="E70" t="n">
         <v>1</v>
       </c>
       <c r="F70" t="n">
-        <v>1500</v>
+        <v>80</v>
       </c>
       <c r="G70" t="n">
-        <v>1500</v>
+        <v>80</v>
       </c>
     </row>
     <row r="71">
@@ -2484,22 +2484,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>大甲金筒17</t>
+          <t>大甲金筒21</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>報價-大甲金筒CBA(12*16)(快速)</t>
+          <t>報價-大甲金筒VBA(15*20)(快速)</t>
         </is>
       </c>
       <c r="E71" t="n">
         <v>1</v>
       </c>
       <c r="F71" t="n">
-        <v>1400</v>
+        <v>1900</v>
       </c>
       <c r="G71" t="n">
-        <v>1400</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="72">
@@ -2513,22 +2513,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>大甲金筒16</t>
+          <t>大甲金筒20</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>報價-大甲金筒BA(15*20)(一般)</t>
+          <t>報價-大甲金筒VBA(13*20)(快速)</t>
         </is>
       </c>
       <c r="E72" t="n">
         <v>1</v>
       </c>
       <c r="F72" t="n">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="G72" t="n">
-        <v>1500</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="73">
@@ -2542,22 +2542,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>大甲金筒09</t>
+          <t>大甲金筒19</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>報價-大甲金筒4AC(中)(B)</t>
+          <t>報價-大甲金筒CBA(15*20)(快速)</t>
         </is>
       </c>
       <c r="E73" t="n">
         <v>1</v>
       </c>
       <c r="F73" t="n">
-        <v>400</v>
+        <v>1600</v>
       </c>
       <c r="G73" t="n">
-        <v>400</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="74">
@@ -2571,22 +2571,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>大甲金筒14</t>
+          <t>大甲金筒18</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>報價-大甲金筒BA(12*16)(一般)</t>
+          <t>報價-大甲金筒CBA(13*20)(快速)</t>
         </is>
       </c>
       <c r="E74" t="n">
         <v>1</v>
       </c>
       <c r="F74" t="n">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="G74" t="n">
-        <v>1300</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="75">
@@ -2600,22 +2600,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>大甲金筒13</t>
+          <t>大甲金筒17</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>報價-大甲金筒4AC(特大)(B)</t>
+          <t>報價-大甲金筒CBA(12*16)(快速)</t>
         </is>
       </c>
       <c r="E75" t="n">
         <v>1</v>
       </c>
       <c r="F75" t="n">
-        <v>700</v>
+        <v>1400</v>
       </c>
       <c r="G75" t="n">
-        <v>700</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="76">
@@ -2629,22 +2629,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>大甲金筒12</t>
+          <t>大甲金筒11</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>報價-大甲金筒4AC(LL)(B)</t>
+          <t>報價-大甲金筒4AC(XL)(B)</t>
         </is>
       </c>
       <c r="E76" t="n">
         <v>1</v>
       </c>
       <c r="F76" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="G76" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row r="77">
@@ -2658,22 +2658,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>大甲金筒11</t>
+          <t>大甲金筒15</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>報價-大甲金筒4AC(XL)(B)</t>
+          <t>報價-大甲金筒BA(13*20)(一般)</t>
         </is>
       </c>
       <c r="E77" t="n">
         <v>1</v>
       </c>
       <c r="F77" t="n">
-        <v>500</v>
+        <v>1400</v>
       </c>
       <c r="G77" t="n">
-        <v>500</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="78">
@@ -2687,22 +2687,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>大甲金筒10</t>
+          <t>大甲金筒14</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>報價-大甲金筒4AC(大)(B)</t>
+          <t>報價-大甲金筒BA(12*16)(一般)</t>
         </is>
       </c>
       <c r="E78" t="n">
         <v>1</v>
       </c>
       <c r="F78" t="n">
-        <v>450</v>
+        <v>1300</v>
       </c>
       <c r="G78" t="n">
-        <v>450</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="79">
@@ -2716,22 +2716,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>大甲金筒24</t>
+          <t>大甲金筒13</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>報價-大甲金筒3A(中)(B)</t>
+          <t>報價-大甲金筒4AC(特大)(B)</t>
         </is>
       </c>
       <c r="E79" t="n">
         <v>1</v>
       </c>
       <c r="F79" t="n">
-        <v>450</v>
+        <v>700</v>
       </c>
       <c r="G79" t="n">
-        <v>450</v>
+        <v>700</v>
       </c>
     </row>
     <row r="80">
@@ -2745,22 +2745,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>大甲金筒08</t>
+          <t>大甲金筒12</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>報價-大甲金筒4AC(小)(B)</t>
+          <t>報價-大甲金筒4AC(LL)(B)</t>
         </is>
       </c>
       <c r="E80" t="n">
         <v>1</v>
       </c>
       <c r="F80" t="n">
-        <v>350</v>
+        <v>600</v>
       </c>
       <c r="G80" t="n">
-        <v>350</v>
+        <v>600</v>
       </c>
     </row>
     <row r="81">
@@ -2774,22 +2774,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>大甲金筒07-1</t>
+          <t>大甲金筒24-1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>報價-大甲金筒蓋子4A(特大)(尺6)(B)(蓋子)</t>
+          <t>報價-大甲金筒3A(中)(B)(蓋子)</t>
         </is>
       </c>
       <c r="E81" t="n">
         <v>1</v>
       </c>
       <c r="F81" t="n">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="G81" t="n">
-        <v>150</v>
+        <v>90</v>
       </c>
     </row>
     <row r="82">
@@ -2803,22 +2803,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>大甲金筒07</t>
+          <t>大甲金筒10</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>報價-大甲金筒4A(特大)(尺6)(B)</t>
+          <t>報價-大甲金筒4AC(大)(B)</t>
         </is>
       </c>
       <c r="E82" t="n">
         <v>1</v>
       </c>
       <c r="F82" t="n">
-        <v>650</v>
+        <v>450</v>
       </c>
       <c r="G82" t="n">
-        <v>650</v>
+        <v>450</v>
       </c>
     </row>
     <row r="83">
@@ -2832,22 +2832,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>大甲金筒06-1</t>
+          <t>大甲金筒09</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>報價-大甲金筒蓋子4A(LL)(尺4)(B)(蓋子)</t>
+          <t>報價-大甲金筒4AC(中)(B)</t>
         </is>
       </c>
       <c r="E83" t="n">
         <v>1</v>
       </c>
       <c r="F83" t="n">
-        <v>120</v>
+        <v>400</v>
       </c>
       <c r="G83" t="n">
-        <v>120</v>
+        <v>400</v>
       </c>
     </row>
     <row r="84">
@@ -2861,22 +2861,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>大甲金筒06</t>
+          <t>大甲金筒08</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>報價-大甲金筒4A(LL)(尺4)(B)</t>
+          <t>報價-大甲金筒4AC(小)(B)</t>
         </is>
       </c>
       <c r="E84" t="n">
         <v>1</v>
       </c>
       <c r="F84" t="n">
-        <v>550</v>
+        <v>350</v>
       </c>
       <c r="G84" t="n">
-        <v>550</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85">
@@ -2890,22 +2890,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>大甲金筒23-1</t>
+          <t>大甲金筒07-1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>報價-大甲金筒3A(小)(B)(蓋子)</t>
+          <t>報價-大甲金筒蓋子4A(特大)(尺6)(B)(蓋子)</t>
         </is>
       </c>
       <c r="E85" t="n">
         <v>1</v>
       </c>
       <c r="F85" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="G85" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
     </row>
     <row r="86">
@@ -2919,22 +2919,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>大甲金筒27-1</t>
+          <t>大甲金筒07</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>報價-大甲金筒3A(LL)(B)(蓋子)</t>
+          <t>報價-大甲金筒4A(特大)(尺6)(B)</t>
         </is>
       </c>
       <c r="E86" t="n">
         <v>1</v>
       </c>
       <c r="F86" t="n">
-        <v>140</v>
+        <v>650</v>
       </c>
       <c r="G86" t="n">
-        <v>140</v>
+        <v>650</v>
       </c>
     </row>
     <row r="87">
@@ -2948,22 +2948,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>大甲金筒24-1</t>
+          <t>大甲金筒24</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>報價-大甲金筒3A(中)(B)(蓋子)</t>
+          <t>報價-大甲金筒3A(中)(B)</t>
         </is>
       </c>
       <c r="E87" t="n">
         <v>1</v>
       </c>
       <c r="F87" t="n">
-        <v>90</v>
+        <v>450</v>
       </c>
       <c r="G87" t="n">
-        <v>90</v>
+        <v>450</v>
       </c>
     </row>
     <row r="88">
@@ -2977,22 +2977,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>大甲金筒34</t>
+          <t>大甲金筒28</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>報價-大甲金筒3AC(特大)(B)</t>
+          <t>報價-大甲金筒3A(特大)(B)</t>
         </is>
       </c>
       <c r="E88" t="n">
         <v>1</v>
       </c>
       <c r="F88" t="n">
-        <v>900</v>
+        <v>850</v>
       </c>
       <c r="G88" t="n">
-        <v>900</v>
+        <v>850</v>
       </c>
     </row>
     <row r="89">
@@ -3006,22 +3006,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>大甲金筒05</t>
+          <t>大甲金筒25</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>報價-大甲金筒4A(XL)(尺3.5)(B)</t>
+          <t>報價-大甲金筒3A(大)(B)</t>
         </is>
       </c>
       <c r="E89" t="n">
         <v>1</v>
       </c>
       <c r="F89" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="G89" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
     </row>
     <row r="90">
@@ -3035,22 +3035,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>大甲金筒42</t>
+          <t>大甲金筒25-1</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>報價-大甲金筒C1(尺6)(C)</t>
+          <t>報價-大甲金筒3A(大)(B)(蓋子)</t>
         </is>
       </c>
       <c r="E90" t="n">
         <v>1</v>
       </c>
       <c r="F90" t="n">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="G90" t="n">
-        <v>1100</v>
+        <v>100</v>
       </c>
     </row>
     <row r="91">
@@ -3064,22 +3064,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>大甲金筒41</t>
+          <t>大甲金筒06</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>報價-大甲金筒C1(尺3)(C)</t>
+          <t>報價-大甲金筒4A(LL)(尺4)(B)</t>
         </is>
       </c>
       <c r="E91" t="n">
         <v>1</v>
       </c>
       <c r="F91" t="n">
-        <v>850</v>
+        <v>550</v>
       </c>
       <c r="G91" t="n">
-        <v>850</v>
+        <v>550</v>
       </c>
     </row>
     <row r="92">
@@ -3093,22 +3093,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>大甲金筒40</t>
+          <t>大甲金筒42</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>報價-大甲金筒C1(尺2)(C)</t>
+          <t>報價-大甲金筒C1(尺6)(C)</t>
         </is>
       </c>
       <c r="E92" t="n">
         <v>1</v>
       </c>
       <c r="F92" t="n">
-        <v>750</v>
+        <v>1100</v>
       </c>
       <c r="G92" t="n">
-        <v>750</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="93">
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>大甲金筒39</t>
+          <t>大甲金筒41</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>報價-大甲金筒08(特大)(XB)</t>
+          <t>報價-大甲金筒C1(尺3)(C)</t>
         </is>
       </c>
       <c r="E93" t="n">
         <v>1</v>
       </c>
       <c r="F93" t="n">
-        <v>750</v>
+        <v>850</v>
       </c>
       <c r="G93" t="n">
-        <v>750</v>
+        <v>850</v>
       </c>
     </row>
     <row r="94">
@@ -3151,22 +3151,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>大甲金筒38</t>
+          <t>大甲金筒40</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>報價-大甲金筒08(LL)(XB)</t>
+          <t>報價-大甲金筒C1(尺2)(C)</t>
         </is>
       </c>
       <c r="E94" t="n">
         <v>1</v>
       </c>
       <c r="F94" t="n">
-        <v>650</v>
+        <v>750</v>
       </c>
       <c r="G94" t="n">
-        <v>650</v>
+        <v>750</v>
       </c>
     </row>
     <row r="95">
@@ -3180,22 +3180,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>大甲金筒37</t>
+          <t>大甲金筒39</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>報價-大甲金筒08(XL)(XB)</t>
+          <t>報價-大甲金筒08(特大)(XB)</t>
         </is>
       </c>
       <c r="E95" t="n">
         <v>1</v>
       </c>
       <c r="F95" t="n">
-        <v>550</v>
+        <v>750</v>
       </c>
       <c r="G95" t="n">
-        <v>550</v>
+        <v>750</v>
       </c>
     </row>
     <row r="96">
@@ -3209,22 +3209,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>大甲金筒36</t>
+          <t>大甲金筒38</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>報價-大甲金筒08(大)(XB)</t>
+          <t>報價-大甲金筒08(LL)(XB)</t>
         </is>
       </c>
       <c r="E96" t="n">
         <v>1</v>
       </c>
       <c r="F96" t="n">
-        <v>500</v>
+        <v>650</v>
       </c>
       <c r="G96" t="n">
-        <v>500</v>
+        <v>650</v>
       </c>
     </row>
     <row r="97">
@@ -3238,22 +3238,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>大甲金筒35</t>
+          <t>大甲金筒37</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>報價-大甲金筒08(中)(XB)</t>
+          <t>報價-大甲金筒08(XL)(XB)</t>
         </is>
       </c>
       <c r="E97" t="n">
         <v>1</v>
       </c>
       <c r="F97" t="n">
-        <v>450</v>
+        <v>550</v>
       </c>
       <c r="G97" t="n">
-        <v>450</v>
+        <v>550</v>
       </c>
     </row>
     <row r="98">
@@ -3267,22 +3267,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>大甲金筒33</t>
+          <t>大甲金筒36</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>報價-大甲金筒3AC(LL)(B)</t>
+          <t>報價-大甲金筒08(大)(XB)</t>
         </is>
       </c>
       <c r="E98" t="n">
         <v>1</v>
       </c>
       <c r="F98" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="G98" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
     </row>
     <row r="99">
@@ -3296,22 +3296,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>大甲金筒25</t>
+          <t>大甲金筒35</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>報價-大甲金筒3A(大)(B)</t>
+          <t>報價-大甲金筒08(中)(XB)</t>
         </is>
       </c>
       <c r="E99" t="n">
         <v>1</v>
       </c>
       <c r="F99" t="n">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="G99" t="n">
-        <v>500</v>
+        <v>450</v>
       </c>
     </row>
     <row r="100">
@@ -3325,22 +3325,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>大甲金筒32</t>
+          <t>大甲金筒34</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>報價-大甲金筒3AC(XL)(B)</t>
+          <t>報價-大甲金筒3AC(特大)(B)</t>
         </is>
       </c>
       <c r="E100" t="n">
         <v>1</v>
       </c>
       <c r="F100" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="G100" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="101">
@@ -3354,22 +3354,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>大甲金筒31</t>
+          <t>大甲金筒33</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>報價-大甲金筒3AC(大)(B)</t>
+          <t>報價-大甲金筒3AC(LL)(B)</t>
         </is>
       </c>
       <c r="E101" t="n">
         <v>1</v>
       </c>
       <c r="F101" t="n">
-        <v>550</v>
+        <v>800</v>
       </c>
       <c r="G101" t="n">
-        <v>550</v>
+        <v>800</v>
       </c>
     </row>
     <row r="102">
@@ -3383,22 +3383,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>大甲金筒30</t>
+          <t>大甲金筒32</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>報價-大甲金筒3AC(中)(B)</t>
+          <t>報價-大甲金筒3AC(XL)(B)</t>
         </is>
       </c>
       <c r="E102" t="n">
         <v>1</v>
       </c>
       <c r="F102" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="G102" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="103">
@@ -3412,22 +3412,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>大甲金筒29</t>
+          <t>大甲金筒31</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>報價-大甲金筒3AC(小)(B)</t>
+          <t>報價-大甲金筒3AC(大)(B)</t>
         </is>
       </c>
       <c r="E103" t="n">
         <v>1</v>
       </c>
       <c r="F103" t="n">
-        <v>450</v>
+        <v>550</v>
       </c>
       <c r="G103" t="n">
-        <v>450</v>
+        <v>550</v>
       </c>
     </row>
     <row r="104">
@@ -3441,22 +3441,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>大甲金筒28-1</t>
+          <t>大甲金筒30</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>報價-大甲金筒3A(特大)(B)(蓋子)</t>
+          <t>報價-大甲金筒3AC(中)(B)</t>
         </is>
       </c>
       <c r="E104" t="n">
         <v>1</v>
       </c>
       <c r="F104" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="G104" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
     </row>
     <row r="105">
@@ -3470,22 +3470,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>大甲金筒28</t>
+          <t>大甲金筒29</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>報價-大甲金筒3A(特大)(B)</t>
+          <t>報價-大甲金筒3AC(小)(B)</t>
         </is>
       </c>
       <c r="E105" t="n">
         <v>1</v>
       </c>
       <c r="F105" t="n">
-        <v>850</v>
+        <v>450</v>
       </c>
       <c r="G105" t="n">
-        <v>850</v>
+        <v>450</v>
       </c>
     </row>
     <row r="106">
@@ -3499,22 +3499,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>大甲金筒27</t>
+          <t>大甲金筒28-1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>報價-大甲金筒3A(LL)(B)</t>
+          <t>報價-大甲金筒3A(特大)(B)(蓋子)</t>
         </is>
       </c>
       <c r="E106" t="n">
         <v>1</v>
       </c>
       <c r="F106" t="n">
-        <v>750</v>
+        <v>160</v>
       </c>
       <c r="G106" t="n">
-        <v>750</v>
+        <v>160</v>
       </c>
     </row>
     <row r="107">
@@ -3528,22 +3528,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>大甲金筒26</t>
+          <t>大甲金筒27-1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>報價-大甲金筒3A(XL)(B)</t>
+          <t>報價-大甲金筒3A(LL)(B)(蓋子)</t>
         </is>
       </c>
       <c r="E107" t="n">
         <v>1</v>
       </c>
       <c r="F107" t="n">
-        <v>550</v>
+        <v>140</v>
       </c>
       <c r="G107" t="n">
-        <v>550</v>
+        <v>140</v>
       </c>
     </row>
     <row r="108">
@@ -3557,22 +3557,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>大甲金筒25-1</t>
+          <t>大甲金筒27</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>報價-大甲金筒3A(大)(B)(蓋子)</t>
+          <t>報價-大甲金筒3A(LL)(B)</t>
         </is>
       </c>
       <c r="E108" t="n">
         <v>1</v>
       </c>
       <c r="F108" t="n">
-        <v>100</v>
+        <v>750</v>
       </c>
       <c r="G108" t="n">
-        <v>100</v>
+        <v>750</v>
       </c>
     </row>
     <row r="109">
@@ -3586,22 +3586,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>大甲金筒05-1</t>
+          <t>大甲金筒26</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>報價-大甲金筒蓋子4A(XL)(尺3.5)(B)(蓋子)</t>
+          <t>報價-大甲金筒3A(XL)(B)</t>
         </is>
       </c>
       <c r="E109" t="n">
         <v>1</v>
       </c>
       <c r="F109" t="n">
-        <v>100</v>
+        <v>550</v>
       </c>
       <c r="G109" t="n">
-        <v>100</v>
+        <v>550</v>
       </c>
     </row>
     <row r="110">
@@ -3615,22 +3615,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>大甲金筒04-1</t>
+          <t>大甲金筒06-1</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>報價-大甲金筒蓋子4A(大)(尺3)(B)(蓋子)</t>
+          <t>報價-大甲金筒蓋子4A(LL)(尺4)(B)(蓋子)</t>
         </is>
       </c>
       <c r="E110" t="n">
         <v>1</v>
       </c>
       <c r="F110" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="G110" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
     <row r="111">
@@ -3644,22 +3644,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>大甲金筒04</t>
+          <t>大甲金筒05-1</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>報價-大甲金筒4A(大)(尺3)(B)</t>
+          <t>報價-大甲金筒蓋子4A(XL)(尺3.5)(B)(蓋子)</t>
         </is>
       </c>
       <c r="E111" t="n">
         <v>1</v>
       </c>
       <c r="F111" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="G111" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
     </row>
     <row r="112">
@@ -3673,22 +3673,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>大甲金筒01-1</t>
+          <t>大甲金筒05</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>報價-大甲金筒蓋子4As(9吋)(B)(蓋子)</t>
+          <t>報價-大甲金筒4A(XL)(尺3.5)(B)</t>
         </is>
       </c>
       <c r="E112" t="n">
         <v>1</v>
       </c>
       <c r="F112" t="n">
-        <v>60</v>
+        <v>450</v>
       </c>
       <c r="G112" t="n">
-        <v>60</v>
+        <v>450</v>
       </c>
     </row>
     <row r="113">
@@ -3702,22 +3702,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>RE32</t>
+          <t>大甲金筒02</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>尺3微煙TG3沉(1.1)10斤</t>
+          <t>報價-大甲金筒4A(小)(尺1)(B)</t>
         </is>
       </c>
       <c r="E113" t="n">
         <v>1</v>
       </c>
       <c r="F113" t="n">
-        <v>2000</v>
+        <v>300</v>
       </c>
       <c r="G113" t="n">
-        <v>2000</v>
+        <v>300</v>
       </c>
     </row>
     <row r="114">
@@ -3731,22 +3731,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>L069</t>
+          <t>RE32</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>(小)竹福金50支G9-S</t>
+          <t>尺3微煙TG3沉(1.1)10斤</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F114" t="n">
-        <v>230</v>
+        <v>2000</v>
       </c>
       <c r="G114" t="n">
-        <v>2300</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="115">
@@ -3760,22 +3760,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>D003</t>
+          <t>L069</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>(紅)補運錢40支</t>
+          <t>(小)竹福金50支G9-S</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F115" t="n">
-        <v>310</v>
+        <v>230</v>
       </c>
       <c r="G115" t="n">
-        <v>1550</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="116">
@@ -3789,22 +3789,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>大甲金筒01</t>
+          <t>D003</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>報價-大甲金筒4As(9吋)(B)</t>
+          <t>(紅)補運錢40支</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F116" t="n">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="G116" t="n">
-        <v>250</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="117">
@@ -3847,22 +3847,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>大甲金筒02</t>
+          <t>大甲金筒01-1</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>報價-大甲金筒4A(小)(尺1)(B)</t>
+          <t>報價-大甲金筒蓋子4As(9吋)(B)(蓋子)</t>
         </is>
       </c>
       <c r="E118" t="n">
         <v>1</v>
       </c>
       <c r="F118" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="G118" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
     </row>
     <row r="119">
@@ -3876,22 +3876,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>大甲金筒02-1</t>
+          <t>大甲金筒01</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>報價-大甲金筒蓋子4A(小)(尺1)(B)(蓋子)</t>
+          <t>報價-大甲金筒4As(9吋)(B)</t>
         </is>
       </c>
       <c r="E119" t="n">
         <v>1</v>
       </c>
       <c r="F119" t="n">
-        <v>70</v>
+        <v>250</v>
       </c>
       <c r="G119" t="n">
-        <v>70</v>
+        <v>250</v>
       </c>
     </row>
     <row r="120">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>大甲金筒03</t>
+          <t>大甲金筒02-1</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>報價-大甲金筒4A(中)(尺2)(B)</t>
+          <t>報價-大甲金筒蓋子4A(小)(尺1)(B)(蓋子)</t>
         </is>
       </c>
       <c r="E120" t="n">
         <v>1</v>
       </c>
       <c r="F120" t="n">
-        <v>350</v>
+        <v>70</v>
       </c>
       <c r="G120" t="n">
-        <v>350</v>
+        <v>70</v>
       </c>
     </row>
     <row r="121">
@@ -3934,28 +3934,28 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>大甲金筒03-1</t>
+          <t>大甲金筒03</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>報價-大甲金筒蓋子4A(中)(尺2)(B)(蓋子)</t>
+          <t>報價-大甲金筒4A(中)(尺2)(B)</t>
         </is>
       </c>
       <c r="E121" t="n">
         <v>1</v>
       </c>
       <c r="F121" t="n">
-        <v>80</v>
+        <v>350</v>
       </c>
       <c r="G121" t="n">
-        <v>80</v>
+        <v>350</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026/01/20</t>
+          <t>2026/01/29</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -3963,28 +3963,28 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>L044</t>
+          <t>大甲金筒03-1</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>竹神甲馬20支</t>
+          <t>報價-大甲金筒蓋子4A(中)(尺2)(B)(蓋子)</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F122" t="n">
-        <v>205</v>
+        <v>80</v>
       </c>
       <c r="G122" t="n">
-        <v>615</v>
+        <v>80</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026/01/20</t>
+          <t>2026/01/29</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -3992,28 +3992,28 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>YE01</t>
+          <t>大甲金筒04</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>冥元台幣(30入)</t>
+          <t>報價-大甲金筒4A(大)(尺3)(B)</t>
         </is>
       </c>
       <c r="E123" t="n">
         <v>1</v>
       </c>
       <c r="F123" t="n">
-        <v>510</v>
+        <v>400</v>
       </c>
       <c r="G123" t="n">
-        <v>510</v>
+        <v>400</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026/01/20</t>
+          <t>2026/01/29</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -4021,22 +4021,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>大甲金筒04-1</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>天庫80支</t>
+          <t>報價-大甲金筒蓋子4A(大)(尺3)(B)(蓋子)</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F124" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="G124" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
     </row>
     <row r="125">
@@ -4050,22 +4050,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>L044</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>地庫80支</t>
+          <t>竹神甲馬20支</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F125" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="G125" t="n">
-        <v>1000</v>
+        <v>615</v>
       </c>
     </row>
     <row r="126">
@@ -4079,22 +4079,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>YE01</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>水庫80支</t>
+          <t>冥元台幣(30入)</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F126" t="n">
-        <v>200</v>
+        <v>510</v>
       </c>
       <c r="G126" t="n">
-        <v>1000</v>
+        <v>510</v>
       </c>
     </row>
     <row r="127">
@@ -4108,22 +4108,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>L063</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>竹彩面大壽金20支K1</t>
+          <t>天庫80支</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F127" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="G127" t="n">
-        <v>630</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="128">
@@ -4137,22 +4137,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>L068</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>(小)竹四方金48支G5-S</t>
+          <t>地庫80支</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F128" t="n">
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="G128" t="n">
-        <v>4500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="129">
@@ -4166,22 +4166,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>X007</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>B(長)中壽黃-蓮花版</t>
+          <t>水庫80支</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F129" t="n">
-        <v>310</v>
+        <v>200</v>
       </c>
       <c r="G129" t="n">
-        <v>620</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="130">
@@ -4195,22 +4195,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>A001</t>
+          <t>L063</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>壽生(6千)送錯未收貨</t>
+          <t>竹彩面大壽金20支K1</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F130" t="n">
-        <v>290</v>
+        <v>210</v>
       </c>
       <c r="G130" t="n">
-        <v>290</v>
+        <v>630</v>
       </c>
     </row>
     <row r="131">
@@ -4224,22 +4224,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>L037</t>
+          <t>L068</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>台北環保壽金48支</t>
+          <t>(小)竹四方金48支G5-S</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F131" t="n">
-        <v>120</v>
+        <v>225</v>
       </c>
       <c r="G131" t="n">
-        <v>240</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="132">
@@ -4253,28 +4253,28 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>L038</t>
+          <t>X007</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>台北環保刈金48支</t>
+          <t>B(長)中壽黃-蓮花版</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F132" t="n">
-        <v>120</v>
+        <v>310</v>
       </c>
       <c r="G132" t="n">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026/01/15</t>
+          <t>2026/01/20</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -4282,28 +4282,28 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>鑫東記11</t>
+          <t>A001</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>四季10香環(60入)</t>
+          <t>壽生(6千)送錯未收貨</t>
         </is>
       </c>
       <c r="E133" t="n">
         <v>1</v>
       </c>
       <c r="F133" t="n">
-        <v>40</v>
+        <v>290</v>
       </c>
       <c r="G133" t="n">
-        <v>40</v>
+        <v>290</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026/01/15</t>
+          <t>2026/01/20</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -4311,28 +4311,28 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>鑫東記08</t>
+          <t>L037</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>桂香尺6(40斤)</t>
+          <t>台北環保壽金48支</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F134" t="n">
-        <v>28</v>
+        <v>120</v>
       </c>
       <c r="G134" t="n">
-        <v>28</v>
+        <v>240</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026/01/15</t>
+          <t>2026/01/20</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>鑫東記09</t>
+          <t>L038</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>A特沉料尺3(40斤)(香)</t>
+          <t>台北環保刈金48支</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F135" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="G135" t="n">
-        <v>70</v>
+        <v>600</v>
       </c>
     </row>
     <row r="136">
@@ -4369,22 +4369,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>鑫東記07</t>
+          <t>鑫東記10</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>桂香尺3(40斤)</t>
+          <t>A特沉料尺6(40斤)(香)</t>
         </is>
       </c>
       <c r="E136" t="n">
         <v>1</v>
       </c>
       <c r="F136" t="n">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="G136" t="n">
-        <v>28</v>
+        <v>70</v>
       </c>
     </row>
     <row r="137">
@@ -4398,22 +4398,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>鑫東記10</t>
+          <t>鑫東記07</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>A特沉料尺6(40斤)(香)</t>
+          <t>桂香尺3(40斤)</t>
         </is>
       </c>
       <c r="E137" t="n">
         <v>1</v>
       </c>
       <c r="F137" t="n">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="G137" t="n">
-        <v>70</v>
+        <v>28</v>
       </c>
     </row>
     <row r="138">
@@ -4427,22 +4427,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>鑫東記13</t>
+          <t>鑫東記09</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>富貴沉A尺6(香)</t>
+          <t>A特沉料尺3(40斤)(香)</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F138" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G138" t="n">
-        <v>800</v>
+        <v>70</v>
       </c>
     </row>
     <row r="139">
@@ -4456,28 +4456,28 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>鑫東記12</t>
+          <t>鑫東記08</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>富貴沉A尺3(香)</t>
+          <t>桂香尺6(40斤)</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="F139" t="n">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="G139" t="n">
-        <v>1600</v>
+        <v>28</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026/01/11</t>
+          <t>2026/01/15</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -4485,28 +4485,28 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>PK07</t>
+          <t>鑫東記11</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>福鼎福金(金箔)60支</t>
+          <t>四季10香環(60入)</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F140" t="n">
-        <v>570</v>
+        <v>40</v>
       </c>
       <c r="G140" t="n">
-        <v>2850</v>
+        <v>40</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026/01/11</t>
+          <t>2026/01/15</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -4514,28 +4514,28 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>PK06</t>
+          <t>鑫東記12</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>福鼎四方金(金箔)60支</t>
+          <t>富貴沉A尺3(香)</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F141" t="n">
-        <v>570</v>
+        <v>80</v>
       </c>
       <c r="G141" t="n">
-        <v>2850</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026/01/11</t>
+          <t>2026/01/15</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -4543,28 +4543,28 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>PK05</t>
+          <t>鑫東記13</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>福鼎壽金(金箔)60支</t>
+          <t>富貴沉A尺6(香)</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F142" t="n">
-        <v>570</v>
+        <v>80</v>
       </c>
       <c r="G142" t="n">
-        <v>2850</v>
+        <v>800</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026/01/05</t>
+          <t>2026/01/11</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -4572,28 +4572,28 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>J019</t>
+          <t>PK07</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>(四方)地藏王30支</t>
+          <t>福鼎福金(金箔)60支</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F143" t="n">
-        <v>390</v>
+        <v>570</v>
       </c>
       <c r="G143" t="n">
-        <v>390</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026/01/05</t>
+          <t>2026/01/11</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -4601,28 +4601,28 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>B006</t>
+          <t>PK06</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>(本色)古紙40支</t>
+          <t>福鼎四方金(金箔)60支</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F144" t="n">
-        <v>440</v>
+        <v>570</v>
       </c>
       <c r="G144" t="n">
-        <v>1320</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026/01/05</t>
+          <t>2026/01/11</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -4630,28 +4630,28 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>RA32</t>
+          <t>PK05</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2尺八方螺旋香12hr</t>
+          <t>福鼎壽金(金箔)60支</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F145" t="n">
-        <v>350</v>
+        <v>570</v>
       </c>
       <c r="G145" t="n">
-        <v>1050</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026/01/03</t>
+          <t>2026/01/05</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -4659,28 +4659,28 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>G002</t>
+          <t>J019</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>台中粗四方60支</t>
+          <t>(四方)地藏王30支</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F146" t="n">
-        <v>205</v>
+        <v>390</v>
       </c>
       <c r="G146" t="n">
-        <v>1640</v>
+        <v>390</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026/01/03</t>
+          <t>2026/01/05</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -4688,28 +4688,28 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>G001</t>
+          <t>B006</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>台中粗壽金30支</t>
+          <t>(本色)古紙40支</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F147" t="n">
-        <v>205</v>
+        <v>440</v>
       </c>
       <c r="G147" t="n">
-        <v>1640</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026/01/03</t>
+          <t>2026/01/05</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -4717,28 +4717,28 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>L045</t>
+          <t>RA32</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>竹庫錢50支</t>
+          <t>2尺八方螺旋香12hr</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="F148" t="n">
-        <v>195</v>
+        <v>350</v>
       </c>
       <c r="G148" t="n">
-        <v>3120</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026/01/02</t>
+          <t>2026/01/03</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -4746,28 +4746,28 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>P114</t>
+          <t>G002</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>7640寵物金40入</t>
+          <t>台中粗四方60支</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F149" t="n">
-        <v>850</v>
+        <v>205</v>
       </c>
       <c r="G149" t="n">
-        <v>850</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026/01/02</t>
+          <t>2026/01/03</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -4775,28 +4775,28 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>L045</t>
+          <t>G001</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>竹庫錢50支</t>
+          <t>台中粗壽金30支</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F150" t="n">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="G150" t="n">
-        <v>4290</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026/01/02</t>
+          <t>2026/01/03</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -4804,22 +4804,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>L074</t>
+          <t>L045</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>竹小往生24入</t>
+          <t>竹庫錢50支</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F151" t="n">
-        <v>230</v>
+        <v>195</v>
       </c>
       <c r="G151" t="n">
-        <v>1150</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="152">
@@ -4833,109 +4833,109 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>PN27</t>
+          <t>P114</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>*075超拔寵物金40盒</t>
+          <t>7640寵物金40入</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F152" t="n">
-        <v>810</v>
+        <v>850</v>
       </c>
       <c r="G152" t="n">
-        <v>-810</v>
+        <v>850</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2025/12/30</t>
+          <t>2026/01/02</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>PN27</t>
+          <t>L045</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>*075超拔寵物金40盒</t>
+          <t>竹庫錢50支</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="F153" t="n">
-        <v>810</v>
+        <v>195</v>
       </c>
       <c r="G153" t="n">
-        <v>810</v>
+        <v>4290</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2025/12/30</t>
+          <t>2026/01/02</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>L064</t>
+          <t>PN27</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>竹大壽生6入</t>
+          <t>*075超拔寵物金40盒</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="F154" t="n">
-        <v>230</v>
+        <v>810</v>
       </c>
       <c r="G154" t="n">
-        <v>460</v>
+        <v>-810</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2025/12/30</t>
+          <t>2026/01/02</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>A001</t>
+          <t>L074</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>壽生(6千)</t>
+          <t>竹小往生24入</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F155" t="n">
-        <v>290</v>
+        <v>230</v>
       </c>
       <c r="G155" t="n">
-        <v>290</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="156">
@@ -4949,28 +4949,28 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>L056</t>
+          <t>PN27</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>竹彩面五路18支</t>
+          <t>*075超拔寵物金40盒</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F156" t="n">
-        <v>320</v>
+        <v>810</v>
       </c>
       <c r="G156" t="n">
-        <v>960</v>
+        <v>810</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2025/12/27</t>
+          <t>2025/12/30</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -4978,28 +4978,28 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>SHOP3</t>
+          <t>L064</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>蝦皮-大師手作-小盤香香爐1個</t>
+          <t>竹大壽生6入</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F157" t="n">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="G157" t="n">
-        <v>195</v>
+        <v>460</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2025/12/27</t>
+          <t>2025/12/30</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -5007,28 +5007,28 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>SHOP2</t>
+          <t>A001</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>蝦皮-萬代-金普牌-J361手握式噴火槍專用瓦斯3個</t>
+          <t>壽生(6千)</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F158" t="n">
-        <v>135</v>
+        <v>290</v>
       </c>
       <c r="G158" t="n">
-        <v>270</v>
+        <v>290</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2025/12/26</t>
+          <t>2025/12/30</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -5036,28 +5036,28 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>SHOP1</t>
+          <t>L056</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>蝦皮-隆盛行-便爐(小)</t>
+          <t>竹彩面五路18支</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F159" t="n">
-        <v>135</v>
+        <v>320</v>
       </c>
       <c r="G159" t="n">
-        <v>675</v>
+        <v>960</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2025/12/21</t>
+          <t>2025/12/27</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -5065,28 +5065,28 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>D003</t>
+          <t>SHOP3</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>(紅)補運錢40支</t>
+          <t>蝦皮-大師手作-小盤香香爐1個</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F160" t="n">
-        <v>305</v>
+        <v>195</v>
       </c>
       <c r="G160" t="n">
-        <v>1525</v>
+        <v>195</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2025/12/21</t>
+          <t>2025/12/27</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -5094,28 +5094,28 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>L055</t>
+          <t>SHOP2</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>竹壽金(5只)30支</t>
+          <t>蝦皮-萬代-金普牌-J361手握式噴火槍專用瓦斯3個</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F161" t="n">
-        <v>290</v>
+        <v>135</v>
       </c>
       <c r="G161" t="n">
-        <v>2900</v>
+        <v>270</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2025/12/21</t>
+          <t>2025/12/26</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -5123,22 +5123,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>L068</t>
+          <t>SHOP1</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>(小)竹四方金48支G5-S</t>
+          <t>蝦皮-隆盛行-便爐(小)</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F162" t="n">
-        <v>225</v>
+        <v>135</v>
       </c>
       <c r="G162" t="n">
-        <v>4500</v>
+        <v>675</v>
       </c>
     </row>
     <row r="163">
@@ -5152,22 +5152,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>WB02</t>
+          <t>D003</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>3號防風燭80入</t>
+          <t>(紅)補運錢40支</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F163" t="n">
-        <v>800</v>
+        <v>305</v>
       </c>
       <c r="G163" t="n">
-        <v>800</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="164">
@@ -5181,22 +5181,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>L057</t>
+          <t>L055</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>竹彩面土地公18支</t>
+          <t>竹壽金(5只)30支</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F164" t="n">
-        <v>320</v>
+        <v>290</v>
       </c>
       <c r="G164" t="n">
-        <v>640</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="165">
@@ -5210,22 +5210,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>WB01</t>
+          <t>L068</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>(安全)防風燈50對</t>
+          <t>(小)竹四方金48支G5-S</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="F165" t="n">
-        <v>600</v>
+        <v>225</v>
       </c>
       <c r="G165" t="n">
-        <v>-600</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="166">
@@ -5239,22 +5239,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>PE304</t>
+          <t>L057</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>304大金元寶100盒</t>
+          <t>竹彩面土地公18支</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F166" t="n">
-        <v>20</v>
+        <v>320</v>
       </c>
       <c r="G166" t="n">
-        <v>200</v>
+        <v>640</v>
       </c>
     </row>
     <row r="167">
@@ -5268,28 +5268,28 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>PE0306</t>
+          <t>WB02</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>306大金條100盒</t>
+          <t>3號防風燭80入</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F167" t="n">
-        <v>15</v>
+        <v>800</v>
       </c>
       <c r="G167" t="n">
-        <v>150</v>
+        <v>800</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2025/12/20</t>
+          <t>2025/12/21</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -5297,28 +5297,28 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>NIL</t>
+          <t>WB01</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>金白錢各1</t>
+          <t>(安全)防風燈50對</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="F168" t="n">
-        <v>120</v>
+        <v>600</v>
       </c>
       <c r="G168" t="n">
-        <v>240</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2025/12/20</t>
+          <t>2025/12/21</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -5326,28 +5326,28 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>L067</t>
+          <t>PE304</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>(小)竹壽金(十面)20支</t>
+          <t>304大金元寶100盒</t>
         </is>
       </c>
       <c r="E169" t="n">
         <v>10</v>
       </c>
       <c r="F169" t="n">
-        <v>230</v>
+        <v>20</v>
       </c>
       <c r="G169" t="n">
-        <v>2300</v>
+        <v>200</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2025/12/20</t>
+          <t>2025/12/21</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -5355,28 +5355,28 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>D006</t>
+          <t>PE0306</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>(白三色)花仔錢60支</t>
+          <t>306大金條100盒</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F170" t="n">
-        <v>430</v>
+        <v>15</v>
       </c>
       <c r="G170" t="n">
-        <v>430</v>
+        <v>150</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2025/12/19</t>
+          <t>2025/12/20</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -5384,28 +5384,28 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>I004</t>
+          <t>NIL</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>粗甲馬(10支)</t>
+          <t>金白錢各1</t>
         </is>
       </c>
       <c r="E171" t="n">
         <v>2</v>
       </c>
       <c r="F171" t="n">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="G171" t="n">
-        <v>270</v>
+        <v>240</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2025/12/19</t>
+          <t>2025/12/20</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -5413,28 +5413,28 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>YE02</t>
+          <t>L067</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>冥元美金100(30入)</t>
+          <t>(小)竹壽金(十面)20支</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F172" t="n">
-        <v>490</v>
+        <v>230</v>
       </c>
       <c r="G172" t="n">
-        <v>490</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2025/12/19</t>
+          <t>2025/12/20</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -5442,22 +5442,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>L051</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>竹蓮花金30支G6</t>
+          <t>(白三色)花仔錢60支</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F173" t="n">
-        <v>290</v>
+        <v>430</v>
       </c>
       <c r="G173" t="n">
-        <v>870</v>
+        <v>430</v>
       </c>
     </row>
     <row r="174">
@@ -5471,22 +5471,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>L052</t>
+          <t>I004</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>竹蓮花銀30支G6</t>
+          <t>粗甲馬(10支)</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F174" t="n">
-        <v>290</v>
+        <v>135</v>
       </c>
       <c r="G174" t="n">
-        <v>870</v>
+        <v>270</v>
       </c>
     </row>
     <row r="175">
@@ -5500,12 +5500,12 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>NIL</t>
+          <t>YE02</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>竹漿天尺20支</t>
+          <t>冥元美金100(30入)</t>
         </is>
       </c>
       <c r="E175" t="n">
@@ -5521,7 +5521,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2025/12/17</t>
+          <t>2025/12/19</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -5529,28 +5529,28 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>進益2</t>
+          <t>L051</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>R6特級板沉</t>
+          <t>竹蓮花金30支G6</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F176" t="n">
-        <v>200</v>
+        <v>290</v>
       </c>
       <c r="G176" t="n">
-        <v>2000</v>
+        <v>870</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2025/12/17</t>
+          <t>2025/12/19</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -5558,28 +5558,28 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>進益1</t>
+          <t>L052</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>R3特級板沉</t>
+          <t>竹蓮花銀30支G6</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F177" t="n">
-        <v>200</v>
+        <v>290</v>
       </c>
       <c r="G177" t="n">
-        <v>4000</v>
+        <v>870</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2025/12/16</t>
+          <t>2025/12/19</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -5587,28 +5587,28 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>WB01</t>
+          <t>NIL</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>(安全)防風燈50對</t>
+          <t>竹漿天尺20支</t>
         </is>
       </c>
       <c r="E178" t="n">
         <v>1</v>
       </c>
       <c r="F178" t="n">
-        <v>600</v>
+        <v>490</v>
       </c>
       <c r="G178" t="n">
-        <v>600</v>
+        <v>490</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2025/12/16</t>
+          <t>2025/12/17</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -5616,28 +5616,28 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>進益2</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>日曆(贈送)</t>
+          <t>R6特級板沉</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F179" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G179" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2025/12/10</t>
+          <t>2025/12/17</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -5645,28 +5645,28 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>WA02</t>
+          <t>進益1</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>(2號)旺6對</t>
+          <t>R3特級板沉</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F180" t="n">
-        <v>510</v>
+        <v>200</v>
       </c>
       <c r="G180" t="n">
-        <v>2040</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2025/12/08</t>
+          <t>2025/12/16</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -5674,28 +5674,28 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>G001</t>
+          <t>WB01</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>台中粗壽金30支</t>
+          <t>(安全)防風燈50對</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F181" t="n">
-        <v>205</v>
+        <v>600</v>
       </c>
       <c r="G181" t="n">
-        <v>820</v>
+        <v>600</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2025/12/08</t>
+          <t>2025/12/16</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -5703,28 +5703,28 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>G002</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>台中粗四方60支</t>
+          <t>日曆(贈送)</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F182" t="n">
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="G182" t="n">
-        <v>1230</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2025/12/08</t>
+          <t>2025/12/10</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -5732,22 +5732,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>L071</t>
+          <t>WA02</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>(小)竹銀紙(2只)50支</t>
+          <t>(2號)旺6對</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F183" t="n">
-        <v>220</v>
+        <v>510</v>
       </c>
       <c r="G183" t="n">
-        <v>2200</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="184">
@@ -5761,22 +5761,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>L069</t>
+          <t>G001</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>(小)竹福金50支G9-S</t>
+          <t>台中粗壽金30支</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F184" t="n">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="G184" t="n">
-        <v>1125</v>
+        <v>820</v>
       </c>
     </row>
     <row r="185">
@@ -5790,28 +5790,28 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>L045</t>
+          <t>G002</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>竹庫錢50支'</t>
+          <t>台中粗四方60支</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F185" t="n">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="G185" t="n">
-        <v>975</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2025/12/03</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -5819,28 +5819,28 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>L074</t>
+          <t>L071</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>竹小往生24入</t>
+          <t>(小)竹銀紙(2只)50支</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F186" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="G186" t="n">
-        <v>460</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2025/12/03</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -5848,28 +5848,28 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>D006</t>
+          <t>L069</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>(白三色)花仔錢60支</t>
+          <t>(小)竹福金50支G9-S</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F187" t="n">
-        <v>430</v>
+        <v>225</v>
       </c>
       <c r="G187" t="n">
-        <v>430</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2025/12/02</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -5877,28 +5877,28 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>G007</t>
+          <t>L045</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>粗蓮花金48支</t>
+          <t>竹庫錢50支'</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F188" t="n">
-        <v>225</v>
+        <v>195</v>
       </c>
       <c r="G188" t="n">
-        <v>225</v>
+        <v>975</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2025/12/02</t>
+          <t>2025/12/03</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -5906,28 +5906,28 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>E001</t>
+          <t>L074</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>太極(5張)</t>
+          <t>竹小往生24入</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F189" t="n">
-        <v>720</v>
+        <v>230</v>
       </c>
       <c r="G189" t="n">
-        <v>720</v>
+        <v>460</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2025/12/02</t>
+          <t>2025/12/03</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -5935,22 +5935,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>L037</t>
+          <t>D006</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>台北環保壽金48支</t>
+          <t>(白三色)花仔錢60支</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F190" t="n">
-        <v>120</v>
+        <v>430</v>
       </c>
       <c r="G190" t="n">
-        <v>240</v>
+        <v>430</v>
       </c>
     </row>
     <row r="191">
@@ -5964,22 +5964,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>L038</t>
+          <t>G007</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>台北環保刈金48支</t>
+          <t>粗蓮花金48支</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F191" t="n">
-        <v>120</v>
+        <v>225</v>
       </c>
       <c r="G191" t="n">
-        <v>360</v>
+        <v>225</v>
       </c>
     </row>
     <row r="192">
@@ -5993,22 +5993,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>L064</t>
+          <t>E001</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>竹大壽生6入</t>
+          <t>太極(5張)</t>
         </is>
       </c>
       <c r="E192" t="n">
         <v>1</v>
       </c>
       <c r="F192" t="n">
-        <v>230</v>
+        <v>720</v>
       </c>
       <c r="G192" t="n">
-        <v>230</v>
+        <v>720</v>
       </c>
     </row>
     <row r="193">
@@ -6022,22 +6022,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>L055</t>
+          <t>L037</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>竹壽金(5只)30支</t>
+          <t>台北環保壽金48支</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F193" t="n">
-        <v>290</v>
+        <v>120</v>
       </c>
       <c r="G193" t="n">
-        <v>1450</v>
+        <v>240</v>
       </c>
     </row>
     <row r="194">
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>L068</t>
+          <t>L038</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>(小)竹四方金48支G5-S</t>
+          <t>台北環保刈金48支</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F194" t="n">
-        <v>225</v>
+        <v>120</v>
       </c>
       <c r="G194" t="n">
-        <v>3375</v>
+        <v>360</v>
       </c>
     </row>
     <row r="195">
@@ -6080,22 +6080,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>L069</t>
+          <t>L064</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>(小)竹福金50支G9-S</t>
+          <t>竹大壽生6入</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F195" t="n">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="G195" t="n">
-        <v>1125</v>
+        <v>230</v>
       </c>
     </row>
     <row r="196">
@@ -6109,22 +6109,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>PE505</t>
+          <t>L055</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>50S土地公6盒</t>
+          <t>竹壽金(5只)30支</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F196" t="n">
-        <v>700</v>
+        <v>290</v>
       </c>
       <c r="G196" t="n">
-        <v>700</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="197">
@@ -6138,22 +6138,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>G006</t>
+          <t>L068</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>*粗蓮花銀36支</t>
+          <t>(小)竹四方金48支G5-S</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F197" t="n">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="G197" t="n">
-        <v>210</v>
+        <v>3375</v>
       </c>
     </row>
     <row r="198">
@@ -6167,22 +6167,22 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>TA10</t>
+          <t>L069</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>A634男名牌LV裝40入</t>
+          <t>(小)竹福金50支G9-S</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F198" t="n">
-        <v>50</v>
+        <v>225</v>
       </c>
       <c r="G198" t="n">
-        <v>50</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="199">
@@ -6196,22 +6196,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>D003</t>
+          <t>PE505</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>(紅)補運錢40支</t>
+          <t>50S土地公6盒</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F199" t="n">
-        <v>305</v>
+        <v>700</v>
       </c>
       <c r="G199" t="n">
-        <v>1525</v>
+        <v>700</v>
       </c>
     </row>
     <row r="200">
@@ -6225,22 +6225,22 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>TA02</t>
+          <t>G006</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>A631男恤衫40入</t>
+          <t>*粗蓮花銀36支</t>
         </is>
       </c>
       <c r="E200" t="n">
         <v>1</v>
       </c>
       <c r="F200" t="n">
-        <v>50</v>
+        <v>210</v>
       </c>
       <c r="G200" t="n">
-        <v>50</v>
+        <v>210</v>
       </c>
     </row>
     <row r="201">
@@ -6254,12 +6254,12 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>TA18</t>
+          <t>TA10</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>B159男休閒鞋30入</t>
+          <t>A634男名牌LV裝40入</t>
         </is>
       </c>
       <c r="E201" t="n">
@@ -6283,22 +6283,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>TA22</t>
+          <t>D003</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>B165男波鞋30入</t>
+          <t>(紅)補運錢40支</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F202" t="n">
-        <v>50</v>
+        <v>305</v>
       </c>
       <c r="G202" t="n">
-        <v>50</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="203">
@@ -6312,28 +6312,28 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>TA01</t>
+          <t>TA02</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>A650男西裝40入</t>
+          <t>A631男恤衫40入</t>
         </is>
       </c>
       <c r="E203" t="n">
         <v>1</v>
       </c>
       <c r="F203" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G203" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2025/11/27</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -6341,28 +6341,28 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>B019</t>
+          <t>TA18</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>白毛邊天金50只</t>
+          <t>B159男休閒鞋30入</t>
         </is>
       </c>
       <c r="E204" t="n">
         <v>1</v>
       </c>
       <c r="F204" t="n">
-        <v>550</v>
+        <v>50</v>
       </c>
       <c r="G204" t="n">
-        <v>550</v>
+        <v>50</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2025/11/27</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -6370,28 +6370,28 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>B018</t>
+          <t>TA22</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>白毛邊壽金50只</t>
+          <t>B165男波鞋30入</t>
         </is>
       </c>
       <c r="E205" t="n">
         <v>1</v>
       </c>
       <c r="F205" t="n">
-        <v>550</v>
+        <v>50</v>
       </c>
       <c r="G205" t="n">
-        <v>550</v>
+        <v>50</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2025/11/25</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -6399,28 +6399,28 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>L069</t>
+          <t>TA01</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>(小)竹福金50支G9-S</t>
+          <t>A650男西裝40入</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F206" t="n">
-        <v>225</v>
+        <v>60</v>
       </c>
       <c r="G206" t="n">
-        <v>1125</v>
+        <v>60</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2025/11/25</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -6428,28 +6428,28 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>A001</t>
+          <t>B019</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>壽生(6千)</t>
+          <t>白毛邊天金50只</t>
         </is>
       </c>
       <c r="E207" t="n">
         <v>1</v>
       </c>
       <c r="F207" t="n">
-        <v>290</v>
+        <v>550</v>
       </c>
       <c r="G207" t="n">
-        <v>290</v>
+        <v>550</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2025/11/21</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -6457,28 +6457,28 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>G004</t>
+          <t>B018</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>台中粗銀紙40支</t>
+          <t>白毛邊壽金50只</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F208" t="n">
-        <v>170</v>
+        <v>550</v>
       </c>
       <c r="G208" t="n">
-        <v>340</v>
+        <v>550</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2025/11/21</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -6486,28 +6486,28 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>J019</t>
+          <t>L069</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>(四方)地藏王30支</t>
+          <t>(小)竹福金50支G9-S</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F209" t="n">
-        <v>390</v>
+        <v>225</v>
       </c>
       <c r="G209" t="n">
-        <v>390</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2025/11/21</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -6515,22 +6515,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>G003</t>
+          <t>A001</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>台中粗福金40支</t>
+          <t>壽生(6千)</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F210" t="n">
-        <v>170</v>
+        <v>290</v>
       </c>
       <c r="G210" t="n">
-        <v>340</v>
+        <v>290</v>
       </c>
     </row>
     <row r="211">
@@ -6544,22 +6544,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>G001</t>
+          <t>G004</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>台中粗壽金30支</t>
+          <t>台中粗銀紙40支</t>
         </is>
       </c>
       <c r="E211" t="n">
         <v>2</v>
       </c>
       <c r="F211" t="n">
-        <v>205</v>
+        <v>170</v>
       </c>
       <c r="G211" t="n">
-        <v>410</v>
+        <v>340</v>
       </c>
     </row>
     <row r="212">
@@ -6573,22 +6573,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>G055</t>
+          <t>J019</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>台北刈金50支</t>
+          <t>(四方)地藏王30支</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F212" t="n">
-        <v>185</v>
+        <v>390</v>
       </c>
       <c r="G212" t="n">
-        <v>370</v>
+        <v>390</v>
       </c>
     </row>
     <row r="213">
@@ -6602,28 +6602,28 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>G058</t>
+          <t>G003</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>台北大銀50支</t>
+          <t>台中粗福金40支</t>
         </is>
       </c>
       <c r="E213" t="n">
         <v>2</v>
       </c>
       <c r="F213" t="n">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="G213" t="n">
-        <v>370</v>
+        <v>340</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/11/21</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -6631,28 +6631,28 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>鑫東記04</t>
+          <t>G001</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>板沉尺3(香)</t>
+          <t>台中粗壽金30支</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="F214" t="n">
-        <v>105</v>
+        <v>205</v>
       </c>
       <c r="G214" t="n">
-        <v>3150</v>
+        <v>410</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/11/21</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -6660,28 +6660,28 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>鑫東記02</t>
+          <t>G055</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>41-1-E123極品水沉香(小盤香)(24入)</t>
+          <t>台北刈金50支</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F215" t="n">
-        <v>120</v>
+        <v>185</v>
       </c>
       <c r="G215" t="n">
-        <v>120</v>
+        <v>370</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/11/21</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -6689,22 +6689,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>鑫東記05</t>
+          <t>G058</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>板沉尺6(香)</t>
+          <t>台北大銀50支</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F216" t="n">
-        <v>105</v>
+        <v>185</v>
       </c>
       <c r="G216" t="n">
-        <v>1050</v>
+        <v>370</v>
       </c>
     </row>
     <row r="217">
@@ -6718,22 +6718,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>鑫東記06</t>
+          <t>鑫東記04</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>A特沉料尺3(香)</t>
+          <t>板沉尺3(香)</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F217" t="n">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="G217" t="n">
-        <v>1400</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="218">
@@ -6747,21 +6747,108 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>鑫東記01</t>
+          <t>鑫東記02</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>微煙10A香環(60入)</t>
+          <t>41-1-E123極品水沉香(小盤香)(24入)</t>
         </is>
       </c>
       <c r="E218" t="n">
         <v>1</v>
       </c>
       <c r="F218" t="n">
+        <v>120</v>
+      </c>
+      <c r="G218" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>鑫東記05</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>板沉尺6(香)</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>10</v>
+      </c>
+      <c r="F219" t="n">
+        <v>105</v>
+      </c>
+      <c r="G219" t="n">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>鑫東記06</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>A特沉料尺3(香)</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>20</v>
+      </c>
+      <c r="F220" t="n">
+        <v>70</v>
+      </c>
+      <c r="G220" t="n">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>鑫東記01</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>微煙10A香環(60入)</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>1</v>
+      </c>
+      <c r="F221" t="n">
         <v>45</v>
       </c>
-      <c r="G218" t="n">
+      <c r="G221" t="n">
         <v>45</v>
       </c>
     </row>
@@ -16908,7 +16995,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026/02/12</t>
+          <t>2026/03/02</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -16928,7 +17015,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026/02/14</t>
+          <t>2026/03/02</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -17008,7 +17095,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026/02/22</t>
+          <t>2026/03/02</t>
         </is>
       </c>
       <c r="D36" t="n">
